--- a/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from JP Core Undefine" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
+++ b/jpcore-r4/main/ValueSet-jp-undefined-vs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Immutable</t>
